--- a/output/pdf_financials_xlsx/BURY.xlsx
+++ b/output/pdf_financials_xlsx/BURY.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0665</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0665</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="93">
@@ -2937,7 +2937,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>0.0665</v>
       </c>
